--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118515656</v>
+        <v>118515648</v>
       </c>
       <c r="B5" t="n">
-        <v>90469</v>
+        <v>57290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1023,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585753</v>
+        <v>585818</v>
       </c>
       <c r="R5" t="n">
-        <v>7059888</v>
+        <v>7059868</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1113,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118515680</v>
+        <v>118515656</v>
       </c>
       <c r="B6" t="n">
-        <v>79469</v>
+        <v>90469</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585711</v>
+        <v>585753</v>
       </c>
       <c r="R6" t="n">
-        <v>7059949</v>
+        <v>7059888</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1215,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118515648</v>
+        <v>118515680</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>79469</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,43 +1232,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585818</v>
+        <v>585711</v>
       </c>
       <c r="R7" t="n">
-        <v>7059868</v>
+        <v>7059949</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -2862,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118515643</v>
+        <v>118515646</v>
       </c>
       <c r="B23" t="n">
-        <v>90522</v>
+        <v>79565</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2878,21 +2878,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585849</v>
+        <v>585835</v>
       </c>
       <c r="R23" t="n">
-        <v>7059886</v>
+        <v>7059882</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2964,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118515646</v>
+        <v>118515643</v>
       </c>
       <c r="B24" t="n">
-        <v>79565</v>
+        <v>90522</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2980,21 +2980,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585835</v>
+        <v>585849</v>
       </c>
       <c r="R24" t="n">
-        <v>7059882</v>
+        <v>7059886</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -2862,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118515646</v>
+        <v>118515643</v>
       </c>
       <c r="B23" t="n">
-        <v>79565</v>
+        <v>90522</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2878,21 +2878,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585835</v>
+        <v>585849</v>
       </c>
       <c r="R23" t="n">
-        <v>7059882</v>
+        <v>7059886</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2964,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118515643</v>
+        <v>118515646</v>
       </c>
       <c r="B24" t="n">
-        <v>90522</v>
+        <v>79565</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2980,21 +2980,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585849</v>
+        <v>585835</v>
       </c>
       <c r="R24" t="n">
-        <v>7059886</v>
+        <v>7059882</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118515688</v>
+        <v>118515655</v>
       </c>
       <c r="B4" t="n">
-        <v>90522</v>
+        <v>90451</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585700</v>
+        <v>585757</v>
       </c>
       <c r="R4" t="n">
-        <v>7059843</v>
+        <v>7059916</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118515648</v>
+        <v>118515650</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>90504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585818</v>
+        <v>585790</v>
       </c>
       <c r="R5" t="n">
-        <v>7059868</v>
+        <v>7059854</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1118,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118515656</v>
+        <v>118515688</v>
       </c>
       <c r="B6" t="n">
-        <v>90469</v>
+        <v>90522</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,25 +1125,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585753</v>
+        <v>585700</v>
       </c>
       <c r="R6" t="n">
-        <v>7059888</v>
+        <v>7059843</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118515680</v>
+        <v>118515640</v>
       </c>
       <c r="B7" t="n">
-        <v>79469</v>
+        <v>57306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,38 +1227,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585711</v>
+        <v>586008</v>
       </c>
       <c r="R7" t="n">
-        <v>7059949</v>
+        <v>7059874</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118515660</v>
+        <v>118515665</v>
       </c>
       <c r="B8" t="n">
-        <v>90788</v>
+        <v>90500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585741</v>
+        <v>585733</v>
       </c>
       <c r="R8" t="n">
-        <v>7059884</v>
+        <v>7059947</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118515647</v>
+        <v>118515684</v>
       </c>
       <c r="B9" t="n">
-        <v>97867</v>
+        <v>90504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,25 +1436,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585834</v>
+        <v>585702</v>
       </c>
       <c r="R9" t="n">
-        <v>7059882</v>
+        <v>7059847</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118515678</v>
+        <v>118515689</v>
       </c>
       <c r="B10" t="n">
-        <v>90522</v>
+        <v>95141</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,25 +1538,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585714</v>
+        <v>585690</v>
       </c>
       <c r="R10" t="n">
-        <v>7059881</v>
+        <v>7059859</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118515683</v>
+        <v>118515657</v>
       </c>
       <c r="B12" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1742,25 +1742,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585702</v>
+        <v>585747</v>
       </c>
       <c r="R12" t="n">
-        <v>7059847</v>
+        <v>7059886</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118515641</v>
+        <v>118515644</v>
       </c>
       <c r="B13" t="n">
-        <v>90788</v>
+        <v>95141</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,25 +1844,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586006</v>
+        <v>585840</v>
       </c>
       <c r="R13" t="n">
-        <v>7059877</v>
+        <v>7059891</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118515686</v>
+        <v>118515672</v>
       </c>
       <c r="B14" t="n">
-        <v>82263</v>
+        <v>95141</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1946,25 +1946,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585701</v>
+        <v>585729</v>
       </c>
       <c r="R14" t="n">
-        <v>7059837</v>
+        <v>7059800</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118515665</v>
+        <v>118515649</v>
       </c>
       <c r="B15" t="n">
-        <v>90500</v>
+        <v>95141</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2048,25 +2048,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585733</v>
+        <v>585807</v>
       </c>
       <c r="R15" t="n">
-        <v>7059947</v>
+        <v>7059851</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118515675</v>
+        <v>118515680</v>
       </c>
       <c r="B16" t="n">
-        <v>57290</v>
+        <v>79469</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2150,43 +2150,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585726</v>
+        <v>585711</v>
       </c>
       <c r="R16" t="n">
-        <v>7059803</v>
+        <v>7059949</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2245,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118515649</v>
+        <v>118515683</v>
       </c>
       <c r="B17" t="n">
-        <v>95141</v>
+        <v>90469</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,21 +2256,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585807</v>
+        <v>585702</v>
       </c>
       <c r="R17" t="n">
-        <v>7059851</v>
+        <v>7059847</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2347,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118515657</v>
+        <v>118515652</v>
       </c>
       <c r="B18" t="n">
-        <v>90504</v>
+        <v>90500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2363,21 +2358,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2387,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585747</v>
+        <v>585771</v>
       </c>
       <c r="R18" t="n">
-        <v>7059886</v>
+        <v>7059873</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2449,10 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118515640</v>
+        <v>118515660</v>
       </c>
       <c r="B19" t="n">
-        <v>57306</v>
+        <v>90788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2465,39 +2460,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586008</v>
+        <v>585741</v>
       </c>
       <c r="R19" t="n">
-        <v>7059874</v>
+        <v>7059884</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2556,10 +2546,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118515644</v>
+        <v>118515663</v>
       </c>
       <c r="B20" t="n">
-        <v>95141</v>
+        <v>82263</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2568,25 +2558,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2596,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585840</v>
+        <v>585737</v>
       </c>
       <c r="R20" t="n">
-        <v>7059891</v>
+        <v>7059887</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2658,10 +2648,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118515645</v>
+        <v>118515656</v>
       </c>
       <c r="B21" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2670,25 +2660,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585835</v>
+        <v>585753</v>
       </c>
       <c r="R21" t="n">
-        <v>7059881</v>
+        <v>7059888</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2760,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118515658</v>
+        <v>118515686</v>
       </c>
       <c r="B22" t="n">
-        <v>79565</v>
+        <v>82263</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2776,21 +2766,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2800,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585747</v>
+        <v>585701</v>
       </c>
       <c r="R22" t="n">
-        <v>7059825</v>
+        <v>7059837</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2862,10 +2852,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118515643</v>
+        <v>118515664</v>
       </c>
       <c r="B23" t="n">
-        <v>90522</v>
+        <v>90504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2878,21 +2868,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2902,10 +2892,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585849</v>
+        <v>585733</v>
       </c>
       <c r="R23" t="n">
-        <v>7059886</v>
+        <v>7059947</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2964,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118515646</v>
+        <v>118515678</v>
       </c>
       <c r="B24" t="n">
-        <v>79565</v>
+        <v>90522</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2980,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3004,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585835</v>
+        <v>585714</v>
       </c>
       <c r="R24" t="n">
-        <v>7059882</v>
+        <v>7059881</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3066,7 +3056,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118515642</v>
+        <v>118515648</v>
       </c>
       <c r="B25" t="n">
         <v>57290</v>
@@ -3102,7 +3092,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3111,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585920</v>
+        <v>585818</v>
       </c>
       <c r="R25" t="n">
-        <v>7059861</v>
+        <v>7059868</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3173,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118515651</v>
+        <v>118515668</v>
       </c>
       <c r="B26" t="n">
-        <v>57290</v>
+        <v>90500</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3189,39 +3179,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585781</v>
+        <v>585729</v>
       </c>
       <c r="R26" t="n">
-        <v>7059825</v>
+        <v>7059977</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3280,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118515655</v>
+        <v>118515642</v>
       </c>
       <c r="B27" t="n">
-        <v>90451</v>
+        <v>57290</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3296,34 +3281,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585757</v>
+        <v>585920</v>
       </c>
       <c r="R27" t="n">
-        <v>7059916</v>
+        <v>7059861</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3382,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118515652</v>
+        <v>118515658</v>
       </c>
       <c r="B28" t="n">
-        <v>90500</v>
+        <v>79565</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3398,21 +3388,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,10 +3412,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585771</v>
+        <v>585747</v>
       </c>
       <c r="R28" t="n">
-        <v>7059873</v>
+        <v>7059825</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3484,10 +3474,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118515664</v>
+        <v>118515675</v>
       </c>
       <c r="B29" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3500,34 +3490,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585733</v>
+        <v>585726</v>
       </c>
       <c r="R29" t="n">
-        <v>7059947</v>
+        <v>7059803</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3586,10 +3581,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118515689</v>
+        <v>118515667</v>
       </c>
       <c r="B30" t="n">
-        <v>95141</v>
+        <v>90500</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3598,25 +3593,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2869</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3626,10 +3621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585690</v>
+        <v>585730</v>
       </c>
       <c r="R30" t="n">
-        <v>7059859</v>
+        <v>7059993</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3688,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118515684</v>
+        <v>118515651</v>
       </c>
       <c r="B31" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3704,34 +3699,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585702</v>
+        <v>585781</v>
       </c>
       <c r="R31" t="n">
-        <v>7059847</v>
+        <v>7059825</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118515668</v>
+        <v>118515647</v>
       </c>
       <c r="B32" t="n">
-        <v>90500</v>
+        <v>97867</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3802,25 +3802,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585729</v>
+        <v>585834</v>
       </c>
       <c r="R32" t="n">
-        <v>7059977</v>
+        <v>7059882</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3892,10 +3892,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118515663</v>
+        <v>118515641</v>
       </c>
       <c r="B33" t="n">
-        <v>82263</v>
+        <v>90788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3908,21 +3908,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585737</v>
+        <v>586006</v>
       </c>
       <c r="R33" t="n">
-        <v>7059887</v>
+        <v>7059877</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118515667</v>
+        <v>118515645</v>
       </c>
       <c r="B34" t="n">
-        <v>90500</v>
+        <v>78484</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4010,21 +4010,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585730</v>
+        <v>585835</v>
       </c>
       <c r="R34" t="n">
-        <v>7059993</v>
+        <v>7059881</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4096,10 +4096,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118515672</v>
+        <v>118515646</v>
       </c>
       <c r="B35" t="n">
-        <v>95141</v>
+        <v>79565</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4108,25 +4108,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585729</v>
+        <v>585835</v>
       </c>
       <c r="R35" t="n">
-        <v>7059800</v>
+        <v>7059882</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4198,10 +4198,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118515650</v>
+        <v>118515643</v>
       </c>
       <c r="B36" t="n">
-        <v>90504</v>
+        <v>90522</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4214,21 +4214,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>585790</v>
+        <v>585849</v>
       </c>
       <c r="R36" t="n">
-        <v>7059854</v>
+        <v>7059886</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -3581,10 +3581,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118515667</v>
+        <v>118515647</v>
       </c>
       <c r="B30" t="n">
-        <v>90500</v>
+        <v>97867</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3593,25 +3593,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3621,10 +3621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585730</v>
+        <v>585834</v>
       </c>
       <c r="R30" t="n">
-        <v>7059993</v>
+        <v>7059882</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3683,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118515651</v>
+        <v>118515667</v>
       </c>
       <c r="B31" t="n">
-        <v>57290</v>
+        <v>90500</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3699,39 +3699,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585781</v>
+        <v>585730</v>
       </c>
       <c r="R31" t="n">
-        <v>7059825</v>
+        <v>7059993</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3790,10 +3785,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118515647</v>
+        <v>118515651</v>
       </c>
       <c r="B32" t="n">
-        <v>97867</v>
+        <v>57290</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3802,38 +3797,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585834</v>
+        <v>585781</v>
       </c>
       <c r="R32" t="n">
-        <v>7059882</v>
+        <v>7059825</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118515655</v>
+        <v>118515650</v>
       </c>
       <c r="B4" t="n">
-        <v>90451</v>
+        <v>90504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585757</v>
+        <v>585790</v>
       </c>
       <c r="R4" t="n">
-        <v>7059916</v>
+        <v>7059854</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118515650</v>
+        <v>118515668</v>
       </c>
       <c r="B5" t="n">
-        <v>90504</v>
+        <v>90500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585790</v>
+        <v>585729</v>
       </c>
       <c r="R5" t="n">
-        <v>7059854</v>
+        <v>7059977</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118515688</v>
+        <v>118515646</v>
       </c>
       <c r="B6" t="n">
-        <v>90522</v>
+        <v>79565</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585700</v>
+        <v>585835</v>
       </c>
       <c r="R6" t="n">
-        <v>7059843</v>
+        <v>7059882</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118515640</v>
+        <v>118515665</v>
       </c>
       <c r="B7" t="n">
-        <v>57306</v>
+        <v>90500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,39 +1231,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586008</v>
+        <v>585733</v>
       </c>
       <c r="R7" t="n">
-        <v>7059874</v>
+        <v>7059947</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1322,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118515665</v>
+        <v>118515649</v>
       </c>
       <c r="B8" t="n">
-        <v>90500</v>
+        <v>95141</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,25 +1329,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585733</v>
+        <v>585807</v>
       </c>
       <c r="R8" t="n">
-        <v>7059947</v>
+        <v>7059851</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1424,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118515684</v>
+        <v>118515678</v>
       </c>
       <c r="B9" t="n">
-        <v>90504</v>
+        <v>90522</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585702</v>
+        <v>585714</v>
       </c>
       <c r="R9" t="n">
-        <v>7059847</v>
+        <v>7059881</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118515689</v>
+        <v>118515640</v>
       </c>
       <c r="B10" t="n">
-        <v>95141</v>
+        <v>57306</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,38 +1533,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585690</v>
+        <v>586008</v>
       </c>
       <c r="R10" t="n">
-        <v>7059859</v>
+        <v>7059874</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118515691</v>
+        <v>118515647</v>
       </c>
       <c r="B11" t="n">
-        <v>82263</v>
+        <v>97867</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1640,25 +1640,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585667</v>
+        <v>585834</v>
       </c>
       <c r="R11" t="n">
-        <v>7060020</v>
+        <v>7059882</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118515657</v>
+        <v>118515641</v>
       </c>
       <c r="B12" t="n">
-        <v>90504</v>
+        <v>90788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585747</v>
+        <v>586006</v>
       </c>
       <c r="R12" t="n">
-        <v>7059886</v>
+        <v>7059877</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118515644</v>
+        <v>118515651</v>
       </c>
       <c r="B13" t="n">
-        <v>95141</v>
+        <v>57290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,38 +1844,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585840</v>
+        <v>585781</v>
       </c>
       <c r="R13" t="n">
-        <v>7059891</v>
+        <v>7059825</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1934,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118515672</v>
+        <v>118515645</v>
       </c>
       <c r="B14" t="n">
-        <v>95141</v>
+        <v>78484</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1946,25 +1951,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585729</v>
+        <v>585835</v>
       </c>
       <c r="R14" t="n">
-        <v>7059800</v>
+        <v>7059881</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2036,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118515649</v>
+        <v>118515658</v>
       </c>
       <c r="B15" t="n">
-        <v>95141</v>
+        <v>79565</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2048,25 +2053,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585807</v>
+        <v>585747</v>
       </c>
       <c r="R15" t="n">
-        <v>7059851</v>
+        <v>7059825</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2138,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118515680</v>
+        <v>118515663</v>
       </c>
       <c r="B16" t="n">
-        <v>79469</v>
+        <v>82263</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2150,25 +2155,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585711</v>
+        <v>585737</v>
       </c>
       <c r="R16" t="n">
-        <v>7059949</v>
+        <v>7059887</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2240,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118515683</v>
+        <v>118515642</v>
       </c>
       <c r="B17" t="n">
-        <v>90469</v>
+        <v>57290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2252,38 +2257,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585702</v>
+        <v>585920</v>
       </c>
       <c r="R17" t="n">
-        <v>7059847</v>
+        <v>7059861</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2342,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118515652</v>
+        <v>118515680</v>
       </c>
       <c r="B18" t="n">
-        <v>90500</v>
+        <v>79469</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2354,25 +2364,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2382,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585771</v>
+        <v>585711</v>
       </c>
       <c r="R18" t="n">
-        <v>7059873</v>
+        <v>7059949</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2444,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118515660</v>
+        <v>118515643</v>
       </c>
       <c r="B19" t="n">
-        <v>90788</v>
+        <v>90522</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2460,21 +2470,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2484,10 +2494,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585741</v>
+        <v>585849</v>
       </c>
       <c r="R19" t="n">
-        <v>7059884</v>
+        <v>7059886</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2546,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118515663</v>
+        <v>118515660</v>
       </c>
       <c r="B20" t="n">
-        <v>82263</v>
+        <v>90788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,21 +2572,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585737</v>
+        <v>585741</v>
       </c>
       <c r="R20" t="n">
-        <v>7059887</v>
+        <v>7059884</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2648,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118515656</v>
+        <v>118515664</v>
       </c>
       <c r="B21" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2660,25 +2670,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2688,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585753</v>
+        <v>585733</v>
       </c>
       <c r="R21" t="n">
-        <v>7059888</v>
+        <v>7059947</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2750,10 +2760,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118515686</v>
+        <v>118515656</v>
       </c>
       <c r="B22" t="n">
-        <v>82263</v>
+        <v>90469</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2762,25 +2772,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2790,10 +2800,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585701</v>
+        <v>585753</v>
       </c>
       <c r="R22" t="n">
-        <v>7059837</v>
+        <v>7059888</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2852,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118515664</v>
+        <v>118515648</v>
       </c>
       <c r="B23" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2868,34 +2878,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585733</v>
+        <v>585818</v>
       </c>
       <c r="R23" t="n">
-        <v>7059947</v>
+        <v>7059868</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2954,10 +2969,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118515678</v>
+        <v>118515684</v>
       </c>
       <c r="B24" t="n">
-        <v>90522</v>
+        <v>90504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2970,21 +2985,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +3009,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585714</v>
+        <v>585702</v>
       </c>
       <c r="R24" t="n">
-        <v>7059881</v>
+        <v>7059847</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3056,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118515648</v>
+        <v>118515672</v>
       </c>
       <c r="B25" t="n">
-        <v>57290</v>
+        <v>95141</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3068,43 +3083,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585818</v>
+        <v>585729</v>
       </c>
       <c r="R25" t="n">
-        <v>7059868</v>
+        <v>7059800</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3163,7 +3173,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118515668</v>
+        <v>118515667</v>
       </c>
       <c r="B26" t="n">
         <v>90500</v>
@@ -3203,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585729</v>
+        <v>585730</v>
       </c>
       <c r="R26" t="n">
-        <v>7059977</v>
+        <v>7059993</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3265,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118515642</v>
+        <v>118515652</v>
       </c>
       <c r="B27" t="n">
-        <v>57290</v>
+        <v>90500</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3281,39 +3291,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585920</v>
+        <v>585771</v>
       </c>
       <c r="R27" t="n">
-        <v>7059861</v>
+        <v>7059873</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3372,10 +3377,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118515658</v>
+        <v>118515683</v>
       </c>
       <c r="B28" t="n">
-        <v>79565</v>
+        <v>90469</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3384,25 +3389,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3412,10 +3417,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585747</v>
+        <v>585702</v>
       </c>
       <c r="R28" t="n">
-        <v>7059825</v>
+        <v>7059847</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3474,10 +3479,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118515675</v>
+        <v>118515657</v>
       </c>
       <c r="B29" t="n">
-        <v>57290</v>
+        <v>90504</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3490,39 +3495,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585726</v>
+        <v>585747</v>
       </c>
       <c r="R29" t="n">
-        <v>7059803</v>
+        <v>7059886</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3581,10 +3581,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118515647</v>
+        <v>118515688</v>
       </c>
       <c r="B30" t="n">
-        <v>97867</v>
+        <v>90522</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3593,25 +3593,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3621,10 +3621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585834</v>
+        <v>585700</v>
       </c>
       <c r="R30" t="n">
-        <v>7059882</v>
+        <v>7059843</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3683,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118515667</v>
+        <v>118515655</v>
       </c>
       <c r="B31" t="n">
-        <v>90500</v>
+        <v>90451</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>112</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585730</v>
+        <v>585757</v>
       </c>
       <c r="R31" t="n">
-        <v>7059993</v>
+        <v>7059916</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118515651</v>
+        <v>118515644</v>
       </c>
       <c r="B32" t="n">
-        <v>57290</v>
+        <v>95141</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3797,43 +3797,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585781</v>
+        <v>585840</v>
       </c>
       <c r="R32" t="n">
-        <v>7059825</v>
+        <v>7059891</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3892,10 +3887,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118515641</v>
+        <v>118515675</v>
       </c>
       <c r="B33" t="n">
-        <v>90788</v>
+        <v>57290</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3908,34 +3903,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>586006</v>
+        <v>585726</v>
       </c>
       <c r="R33" t="n">
-        <v>7059877</v>
+        <v>7059803</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118515645</v>
+        <v>118515691</v>
       </c>
       <c r="B34" t="n">
-        <v>78484</v>
+        <v>82263</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4010,21 +4010,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585835</v>
+        <v>585667</v>
       </c>
       <c r="R34" t="n">
-        <v>7059881</v>
+        <v>7060020</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4096,10 +4096,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118515646</v>
+        <v>118515689</v>
       </c>
       <c r="B35" t="n">
-        <v>79565</v>
+        <v>95141</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4108,25 +4108,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585835</v>
+        <v>585690</v>
       </c>
       <c r="R35" t="n">
-        <v>7059882</v>
+        <v>7059859</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4198,10 +4198,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118515643</v>
+        <v>118515686</v>
       </c>
       <c r="B36" t="n">
-        <v>90522</v>
+        <v>82263</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4214,21 +4214,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>585849</v>
+        <v>585701</v>
       </c>
       <c r="R36" t="n">
-        <v>7059886</v>
+        <v>7059837</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118515650</v>
+        <v>118515668</v>
       </c>
       <c r="B4" t="n">
-        <v>90504</v>
+        <v>90507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585790</v>
+        <v>585729</v>
       </c>
       <c r="R4" t="n">
-        <v>7059854</v>
+        <v>7059977</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118515668</v>
+        <v>118515645</v>
       </c>
       <c r="B5" t="n">
-        <v>90500</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585729</v>
+        <v>585835</v>
       </c>
       <c r="R5" t="n">
-        <v>7059977</v>
+        <v>7059881</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118515646</v>
+        <v>118515667</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>90507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585835</v>
+        <v>585730</v>
       </c>
       <c r="R6" t="n">
-        <v>7059882</v>
+        <v>7059993</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118515665</v>
+        <v>118515689</v>
       </c>
       <c r="B7" t="n">
-        <v>90500</v>
+        <v>95148</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585733</v>
+        <v>585690</v>
       </c>
       <c r="R7" t="n">
-        <v>7059947</v>
+        <v>7059859</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118515649</v>
+        <v>118515646</v>
       </c>
       <c r="B8" t="n">
-        <v>95141</v>
+        <v>79572</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,25 +1329,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585807</v>
+        <v>585835</v>
       </c>
       <c r="R8" t="n">
-        <v>7059851</v>
+        <v>7059882</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118515678</v>
+        <v>118515651</v>
       </c>
       <c r="B9" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,34 +1435,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585714</v>
+        <v>585781</v>
       </c>
       <c r="R9" t="n">
-        <v>7059881</v>
+        <v>7059825</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118515640</v>
+        <v>118515641</v>
       </c>
       <c r="B10" t="n">
-        <v>57306</v>
+        <v>90795</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,39 +1542,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586008</v>
+        <v>586006</v>
       </c>
       <c r="R10" t="n">
-        <v>7059874</v>
+        <v>7059877</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118515647</v>
+        <v>118515650</v>
       </c>
       <c r="B11" t="n">
-        <v>97867</v>
+        <v>90511</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1640,25 +1640,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585834</v>
+        <v>585790</v>
       </c>
       <c r="R11" t="n">
-        <v>7059882</v>
+        <v>7059854</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118515641</v>
+        <v>118515678</v>
       </c>
       <c r="B12" t="n">
-        <v>90788</v>
+        <v>90529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586006</v>
+        <v>585714</v>
       </c>
       <c r="R12" t="n">
-        <v>7059877</v>
+        <v>7059881</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1832,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118515651</v>
+        <v>118515642</v>
       </c>
       <c r="B13" t="n">
         <v>57290</v>
@@ -1868,7 +1868,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585781</v>
+        <v>585920</v>
       </c>
       <c r="R13" t="n">
-        <v>7059825</v>
+        <v>7059861</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1939,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118515645</v>
+        <v>118515647</v>
       </c>
       <c r="B14" t="n">
-        <v>78484</v>
+        <v>97874</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,25 +1951,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585835</v>
+        <v>585834</v>
       </c>
       <c r="R14" t="n">
-        <v>7059881</v>
+        <v>7059882</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118515658</v>
+        <v>118515644</v>
       </c>
       <c r="B15" t="n">
-        <v>79565</v>
+        <v>95148</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2053,25 +2053,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585747</v>
+        <v>585840</v>
       </c>
       <c r="R15" t="n">
-        <v>7059825</v>
+        <v>7059891</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118515663</v>
+        <v>118515686</v>
       </c>
       <c r="B16" t="n">
-        <v>82263</v>
+        <v>82270</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585737</v>
+        <v>585701</v>
       </c>
       <c r="R16" t="n">
-        <v>7059887</v>
+        <v>7059837</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118515642</v>
+        <v>118515691</v>
       </c>
       <c r="B17" t="n">
-        <v>57290</v>
+        <v>82270</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,39 +2261,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585920</v>
+        <v>585667</v>
       </c>
       <c r="R17" t="n">
-        <v>7059861</v>
+        <v>7060020</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2352,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118515680</v>
+        <v>118515658</v>
       </c>
       <c r="B18" t="n">
-        <v>79469</v>
+        <v>79572</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2364,25 +2359,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585711</v>
+        <v>585747</v>
       </c>
       <c r="R18" t="n">
-        <v>7059949</v>
+        <v>7059825</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2454,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118515643</v>
+        <v>118515665</v>
       </c>
       <c r="B19" t="n">
-        <v>90522</v>
+        <v>90507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2470,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2494,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585849</v>
+        <v>585733</v>
       </c>
       <c r="R19" t="n">
-        <v>7059886</v>
+        <v>7059947</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2556,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118515660</v>
+        <v>118515683</v>
       </c>
       <c r="B20" t="n">
-        <v>90788</v>
+        <v>90476</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2568,25 +2563,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2596,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585741</v>
+        <v>585702</v>
       </c>
       <c r="R20" t="n">
-        <v>7059884</v>
+        <v>7059847</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2658,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118515664</v>
+        <v>118515672</v>
       </c>
       <c r="B21" t="n">
-        <v>90504</v>
+        <v>95148</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2670,25 +2665,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2693,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585733</v>
+        <v>585729</v>
       </c>
       <c r="R21" t="n">
-        <v>7059947</v>
+        <v>7059800</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2763,7 +2758,7 @@
         <v>118515656</v>
       </c>
       <c r="B22" t="n">
-        <v>90469</v>
+        <v>90476</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2862,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118515648</v>
+        <v>118515688</v>
       </c>
       <c r="B23" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2878,39 +2873,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585818</v>
+        <v>585700</v>
       </c>
       <c r="R23" t="n">
-        <v>7059868</v>
+        <v>7059843</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2969,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118515684</v>
+        <v>118515664</v>
       </c>
       <c r="B24" t="n">
-        <v>90504</v>
+        <v>90511</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3009,10 +2999,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585702</v>
+        <v>585733</v>
       </c>
       <c r="R24" t="n">
-        <v>7059847</v>
+        <v>7059947</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3071,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118515672</v>
+        <v>118515652</v>
       </c>
       <c r="B25" t="n">
-        <v>95141</v>
+        <v>90507</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3083,25 +3073,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2869</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585729</v>
+        <v>585771</v>
       </c>
       <c r="R25" t="n">
-        <v>7059800</v>
+        <v>7059873</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3173,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118515667</v>
+        <v>118515640</v>
       </c>
       <c r="B26" t="n">
-        <v>90500</v>
+        <v>57306</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3189,34 +3179,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585730</v>
+        <v>586008</v>
       </c>
       <c r="R26" t="n">
-        <v>7059993</v>
+        <v>7059874</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3275,10 +3270,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118515652</v>
+        <v>118515660</v>
       </c>
       <c r="B27" t="n">
-        <v>90500</v>
+        <v>90795</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3291,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3315,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585771</v>
+        <v>585741</v>
       </c>
       <c r="R27" t="n">
-        <v>7059873</v>
+        <v>7059884</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3377,10 +3372,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118515683</v>
+        <v>118515649</v>
       </c>
       <c r="B28" t="n">
-        <v>90469</v>
+        <v>95148</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3393,21 +3388,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3417,10 +3412,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585702</v>
+        <v>585807</v>
       </c>
       <c r="R28" t="n">
-        <v>7059847</v>
+        <v>7059851</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3479,10 +3474,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118515657</v>
+        <v>118515675</v>
       </c>
       <c r="B29" t="n">
-        <v>90504</v>
+        <v>57290</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3495,34 +3490,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585747</v>
+        <v>585726</v>
       </c>
       <c r="R29" t="n">
-        <v>7059886</v>
+        <v>7059803</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3581,10 +3581,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118515688</v>
+        <v>118515663</v>
       </c>
       <c r="B30" t="n">
-        <v>90522</v>
+        <v>82270</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3597,21 +3597,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3621,10 +3621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585700</v>
+        <v>585737</v>
       </c>
       <c r="R30" t="n">
-        <v>7059843</v>
+        <v>7059887</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3683,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118515655</v>
+        <v>118515643</v>
       </c>
       <c r="B31" t="n">
-        <v>90451</v>
+        <v>90529</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585757</v>
+        <v>585849</v>
       </c>
       <c r="R31" t="n">
-        <v>7059916</v>
+        <v>7059886</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118515644</v>
+        <v>118515648</v>
       </c>
       <c r="B32" t="n">
-        <v>95141</v>
+        <v>57290</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3797,38 +3797,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585840</v>
+        <v>585818</v>
       </c>
       <c r="R32" t="n">
-        <v>7059891</v>
+        <v>7059868</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3887,10 +3892,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118515675</v>
+        <v>118515680</v>
       </c>
       <c r="B33" t="n">
-        <v>57290</v>
+        <v>79476</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3899,43 +3904,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585726</v>
+        <v>585711</v>
       </c>
       <c r="R33" t="n">
-        <v>7059803</v>
+        <v>7059949</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118515691</v>
+        <v>118515655</v>
       </c>
       <c r="B34" t="n">
-        <v>82263</v>
+        <v>90458</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4010,21 +4010,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585667</v>
+        <v>585757</v>
       </c>
       <c r="R34" t="n">
-        <v>7060020</v>
+        <v>7059916</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4096,10 +4096,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118515689</v>
+        <v>118515684</v>
       </c>
       <c r="B35" t="n">
-        <v>95141</v>
+        <v>90511</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4108,25 +4108,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585690</v>
+        <v>585702</v>
       </c>
       <c r="R35" t="n">
-        <v>7059859</v>
+        <v>7059847</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4198,10 +4198,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118515686</v>
+        <v>118515657</v>
       </c>
       <c r="B36" t="n">
-        <v>82263</v>
+        <v>90511</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4214,21 +4214,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>585701</v>
+        <v>585747</v>
       </c>
       <c r="R36" t="n">
-        <v>7059837</v>
+        <v>7059886</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118515650</v>
+        <v>118515642</v>
       </c>
       <c r="B11" t="n">
-        <v>90511</v>
+        <v>57290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,34 +1644,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585790</v>
+        <v>585920</v>
       </c>
       <c r="R11" t="n">
-        <v>7059854</v>
+        <v>7059861</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1730,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118515678</v>
+        <v>118515650</v>
       </c>
       <c r="B12" t="n">
-        <v>90529</v>
+        <v>90511</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585714</v>
+        <v>585790</v>
       </c>
       <c r="R12" t="n">
-        <v>7059881</v>
+        <v>7059854</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1832,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118515642</v>
+        <v>118515678</v>
       </c>
       <c r="B13" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,39 +1853,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585920</v>
+        <v>585714</v>
       </c>
       <c r="R13" t="n">
-        <v>7059861</v>
+        <v>7059881</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2347,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118515658</v>
+        <v>118515665</v>
       </c>
       <c r="B18" t="n">
-        <v>79572</v>
+        <v>90507</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2363,21 +2363,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585747</v>
+        <v>585733</v>
       </c>
       <c r="R18" t="n">
-        <v>7059825</v>
+        <v>7059947</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118515665</v>
+        <v>118515658</v>
       </c>
       <c r="B19" t="n">
-        <v>90507</v>
+        <v>79572</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2465,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585733</v>
+        <v>585747</v>
       </c>
       <c r="R19" t="n">
-        <v>7059947</v>
+        <v>7059825</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118482867</v>
+        <v>118482918</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585738</v>
+        <v>585770</v>
       </c>
       <c r="R2" t="n">
-        <v>7059787</v>
+        <v>7059800</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118482918</v>
+        <v>118482867</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -828,7 +828,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585770</v>
+        <v>585738</v>
       </c>
       <c r="R3" t="n">
-        <v>7059800</v>
+        <v>7059787</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118515645</v>
+        <v>118515656</v>
       </c>
       <c r="B5" t="n">
-        <v>78491</v>
+        <v>90476</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585835</v>
+        <v>585753</v>
       </c>
       <c r="R5" t="n">
-        <v>7059881</v>
+        <v>7059888</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118515667</v>
+        <v>118515663</v>
       </c>
       <c r="B6" t="n">
-        <v>90507</v>
+        <v>82270</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585730</v>
+        <v>585737</v>
       </c>
       <c r="R6" t="n">
-        <v>7059993</v>
+        <v>7059887</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118515689</v>
+        <v>118515667</v>
       </c>
       <c r="B7" t="n">
-        <v>95148</v>
+        <v>90507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585690</v>
+        <v>585730</v>
       </c>
       <c r="R7" t="n">
-        <v>7059859</v>
+        <v>7059993</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118515646</v>
+        <v>118515645</v>
       </c>
       <c r="B8" t="n">
-        <v>79572</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,7 +1360,7 @@
         <v>585835</v>
       </c>
       <c r="R8" t="n">
-        <v>7059882</v>
+        <v>7059881</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118515651</v>
+        <v>118515644</v>
       </c>
       <c r="B9" t="n">
-        <v>57290</v>
+        <v>95148</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,43 +1431,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585781</v>
+        <v>585840</v>
       </c>
       <c r="R9" t="n">
-        <v>7059825</v>
+        <v>7059891</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118515641</v>
+        <v>118515651</v>
       </c>
       <c r="B10" t="n">
-        <v>90795</v>
+        <v>57290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,34 +1537,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586006</v>
+        <v>585781</v>
       </c>
       <c r="R10" t="n">
-        <v>7059877</v>
+        <v>7059825</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118515650</v>
+        <v>118515652</v>
       </c>
       <c r="B12" t="n">
-        <v>90511</v>
+        <v>90507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585790</v>
+        <v>585771</v>
       </c>
       <c r="R12" t="n">
-        <v>7059854</v>
+        <v>7059873</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1939,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118515647</v>
+        <v>118515658</v>
       </c>
       <c r="B14" t="n">
-        <v>97874</v>
+        <v>79572</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,25 +1951,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585834</v>
+        <v>585747</v>
       </c>
       <c r="R14" t="n">
-        <v>7059882</v>
+        <v>7059825</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118515644</v>
+        <v>118515686</v>
       </c>
       <c r="B15" t="n">
-        <v>95148</v>
+        <v>82270</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2053,25 +2053,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585840</v>
+        <v>585701</v>
       </c>
       <c r="R15" t="n">
-        <v>7059891</v>
+        <v>7059837</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118515686</v>
+        <v>118515684</v>
       </c>
       <c r="B16" t="n">
-        <v>82270</v>
+        <v>90511</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585701</v>
+        <v>585702</v>
       </c>
       <c r="R16" t="n">
-        <v>7059837</v>
+        <v>7059847</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118515691</v>
+        <v>118515646</v>
       </c>
       <c r="B17" t="n">
-        <v>82270</v>
+        <v>79572</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,21 +2261,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585667</v>
+        <v>585835</v>
       </c>
       <c r="R17" t="n">
-        <v>7060020</v>
+        <v>7059882</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2347,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118515665</v>
+        <v>118515648</v>
       </c>
       <c r="B18" t="n">
-        <v>90507</v>
+        <v>57290</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2363,34 +2363,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585733</v>
+        <v>585818</v>
       </c>
       <c r="R18" t="n">
-        <v>7059947</v>
+        <v>7059868</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2449,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118515658</v>
+        <v>118515665</v>
       </c>
       <c r="B19" t="n">
-        <v>79572</v>
+        <v>90507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2465,21 +2470,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2494,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585747</v>
+        <v>585733</v>
       </c>
       <c r="R19" t="n">
-        <v>7059825</v>
+        <v>7059947</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2551,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118515683</v>
+        <v>118515657</v>
       </c>
       <c r="B20" t="n">
-        <v>90476</v>
+        <v>90511</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2563,25 +2568,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2591,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585702</v>
+        <v>585747</v>
       </c>
       <c r="R20" t="n">
-        <v>7059847</v>
+        <v>7059886</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2755,10 +2760,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118515656</v>
+        <v>118515664</v>
       </c>
       <c r="B22" t="n">
-        <v>90476</v>
+        <v>90511</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2767,25 +2772,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2795,10 +2800,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585753</v>
+        <v>585733</v>
       </c>
       <c r="R22" t="n">
-        <v>7059888</v>
+        <v>7059947</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2857,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118515688</v>
+        <v>118515683</v>
       </c>
       <c r="B23" t="n">
-        <v>90529</v>
+        <v>90476</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2869,25 +2874,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2897,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585700</v>
+        <v>585702</v>
       </c>
       <c r="R23" t="n">
-        <v>7059843</v>
+        <v>7059847</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2959,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118515664</v>
+        <v>118515675</v>
       </c>
       <c r="B24" t="n">
-        <v>90511</v>
+        <v>57290</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2975,34 +2980,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585733</v>
+        <v>585726</v>
       </c>
       <c r="R24" t="n">
-        <v>7059947</v>
+        <v>7059803</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3061,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118515652</v>
+        <v>118515643</v>
       </c>
       <c r="B25" t="n">
-        <v>90507</v>
+        <v>90529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3077,21 +3087,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585771</v>
+        <v>585849</v>
       </c>
       <c r="R25" t="n">
-        <v>7059873</v>
+        <v>7059886</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3163,10 +3173,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118515640</v>
+        <v>118515641</v>
       </c>
       <c r="B26" t="n">
-        <v>57306</v>
+        <v>90795</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3179,39 +3189,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586008</v>
+        <v>586006</v>
       </c>
       <c r="R26" t="n">
-        <v>7059874</v>
+        <v>7059877</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3270,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118515660</v>
+        <v>118515655</v>
       </c>
       <c r="B27" t="n">
-        <v>90795</v>
+        <v>90458</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3286,21 +3291,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>112</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3315,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585741</v>
+        <v>585757</v>
       </c>
       <c r="R27" t="n">
-        <v>7059884</v>
+        <v>7059916</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3372,10 +3377,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118515649</v>
+        <v>118515680</v>
       </c>
       <c r="B28" t="n">
-        <v>95148</v>
+        <v>79476</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3388,21 +3393,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2869</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3412,10 +3417,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585807</v>
+        <v>585711</v>
       </c>
       <c r="R28" t="n">
-        <v>7059851</v>
+        <v>7059949</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3474,10 +3479,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118515675</v>
+        <v>118515660</v>
       </c>
       <c r="B29" t="n">
-        <v>57290</v>
+        <v>90795</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3490,39 +3495,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585726</v>
+        <v>585741</v>
       </c>
       <c r="R29" t="n">
-        <v>7059803</v>
+        <v>7059884</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3581,10 +3581,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118515663</v>
+        <v>118515688</v>
       </c>
       <c r="B30" t="n">
-        <v>82270</v>
+        <v>90529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3597,21 +3597,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3621,10 +3621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>585737</v>
+        <v>585700</v>
       </c>
       <c r="R30" t="n">
-        <v>7059887</v>
+        <v>7059843</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3683,10 +3683,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118515643</v>
+        <v>118515650</v>
       </c>
       <c r="B31" t="n">
-        <v>90529</v>
+        <v>90511</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3699,21 +3699,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3723,10 +3723,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>585849</v>
+        <v>585790</v>
       </c>
       <c r="R31" t="n">
-        <v>7059886</v>
+        <v>7059854</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3785,10 +3785,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118515648</v>
+        <v>118515647</v>
       </c>
       <c r="B32" t="n">
-        <v>57290</v>
+        <v>97874</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3797,43 +3797,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>585818</v>
+        <v>585834</v>
       </c>
       <c r="R32" t="n">
-        <v>7059868</v>
+        <v>7059882</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3892,10 +3887,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118515680</v>
+        <v>118515640</v>
       </c>
       <c r="B33" t="n">
-        <v>79476</v>
+        <v>57306</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3904,38 +3899,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>585711</v>
+        <v>586008</v>
       </c>
       <c r="R33" t="n">
-        <v>7059949</v>
+        <v>7059874</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118515655</v>
+        <v>118515691</v>
       </c>
       <c r="B34" t="n">
-        <v>90458</v>
+        <v>82270</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4010,21 +4010,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>585757</v>
+        <v>585667</v>
       </c>
       <c r="R34" t="n">
-        <v>7059916</v>
+        <v>7060020</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4096,10 +4096,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118515684</v>
+        <v>118515649</v>
       </c>
       <c r="B35" t="n">
-        <v>90511</v>
+        <v>95148</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4108,25 +4108,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>585702</v>
+        <v>585807</v>
       </c>
       <c r="R35" t="n">
-        <v>7059847</v>
+        <v>7059851</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4198,10 +4198,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118515657</v>
+        <v>118515689</v>
       </c>
       <c r="B36" t="n">
-        <v>90511</v>
+        <v>95148</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4210,25 +4210,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>585747</v>
+        <v>585690</v>
       </c>
       <c r="R36" t="n">
-        <v>7059886</v>
+        <v>7059859</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -5099,10 +5099,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122755221</v>
+        <v>122758139</v>
       </c>
       <c r="B44" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5115,16 +5115,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585897</v>
+        <v>585743</v>
       </c>
       <c r="R44" t="n">
-        <v>7059846</v>
+        <v>7059982</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5177,9 +5177,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5194,22 +5209,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122758139</v>
+        <v>122755221</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5222,16 +5237,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5251,13 +5266,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585743</v>
+        <v>585897</v>
       </c>
       <c r="R45" t="n">
-        <v>7059982</v>
+        <v>7059846</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5284,24 +5299,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5316,12 +5316,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -4300,7 +4300,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122757637</v>
+        <v>122758257</v>
       </c>
       <c r="B37" t="n">
         <v>57478</v>
@@ -4336,7 +4336,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4345,13 +4345,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585636</v>
+        <v>585735</v>
       </c>
       <c r="R37" t="n">
-        <v>7059970</v>
+        <v>7059987</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4378,24 +4378,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4410,19 +4400,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122757680</v>
+        <v>122757367</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -4467,13 +4457,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>585688</v>
+        <v>585662</v>
       </c>
       <c r="R38" t="n">
-        <v>7059983</v>
+        <v>7059890</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4500,14 +4490,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4522,22 +4522,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122758257</v>
+        <v>122757908</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4550,42 +4550,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>585735</v>
+        <v>585747</v>
       </c>
       <c r="R39" t="n">
-        <v>7059987</v>
+        <v>7059980</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4612,14 +4607,19 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4634,19 +4634,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122756445</v>
+        <v>122757680</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -4691,13 +4691,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585841</v>
+        <v>585688</v>
       </c>
       <c r="R40" t="n">
-        <v>7059850</v>
+        <v>7059983</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4724,24 +4724,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4756,22 +4746,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122757549</v>
+        <v>122755221</v>
       </c>
       <c r="B41" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4784,34 +4774,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585660</v>
+        <v>585897</v>
       </c>
       <c r="R41" t="n">
-        <v>7059938</v>
+        <v>7059846</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4870,10 +4865,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122755167</v>
+        <v>122756445</v>
       </c>
       <c r="B42" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4886,16 +4881,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4915,13 +4910,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585967</v>
+        <v>585841</v>
       </c>
       <c r="R42" t="n">
-        <v>7059854</v>
+        <v>7059850</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4948,9 +4943,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4965,19 +4975,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122757492</v>
+        <v>122757637</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5022,10 +5032,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585665</v>
+        <v>585636</v>
       </c>
       <c r="R43" t="n">
-        <v>7059914</v>
+        <v>7059970</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5057,7 +5067,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5067,7 +5077,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5221,10 +5231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122755221</v>
+        <v>122757549</v>
       </c>
       <c r="B45" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5237,39 +5247,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585897</v>
+        <v>585660</v>
       </c>
       <c r="R45" t="n">
-        <v>7059846</v>
+        <v>7059938</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5328,10 +5333,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122757908</v>
+        <v>122757492</v>
       </c>
       <c r="B46" t="n">
-        <v>82549</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5344,34 +5349,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585747</v>
+        <v>585665</v>
       </c>
       <c r="R46" t="n">
-        <v>7059980</v>
+        <v>7059914</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5403,7 +5413,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5413,7 +5423,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5440,10 +5455,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122757367</v>
+        <v>122755167</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5456,16 +5471,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5485,13 +5500,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585662</v>
+        <v>585967</v>
       </c>
       <c r="R47" t="n">
-        <v>7059890</v>
+        <v>7059854</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5518,24 +5533,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5550,12 +5550,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -4300,10 +4300,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122758257</v>
+        <v>122757908</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4316,42 +4316,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585735</v>
+        <v>585747</v>
       </c>
       <c r="R37" t="n">
-        <v>7059987</v>
+        <v>7059980</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4378,14 +4373,19 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4400,19 +4400,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122757367</v>
+        <v>122756445</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>585662</v>
+        <v>585841</v>
       </c>
       <c r="R38" t="n">
-        <v>7059890</v>
+        <v>7059850</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4534,10 +4534,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122757908</v>
+        <v>122757492</v>
       </c>
       <c r="B39" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4550,34 +4550,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>585747</v>
+        <v>585665</v>
       </c>
       <c r="R39" t="n">
-        <v>7059980</v>
+        <v>7059914</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4609,7 +4614,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4619,7 +4624,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4646,7 +4656,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122757680</v>
+        <v>122757637</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -4691,13 +4701,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585688</v>
+        <v>585636</v>
       </c>
       <c r="R40" t="n">
-        <v>7059983</v>
+        <v>7059970</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4724,14 +4734,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4746,22 +4766,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122755221</v>
+        <v>122758257</v>
       </c>
       <c r="B41" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4774,16 +4794,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4794,7 +4814,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4803,10 +4823,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585897</v>
+        <v>585735</v>
       </c>
       <c r="R41" t="n">
-        <v>7059846</v>
+        <v>7059987</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4839,6 +4859,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4865,7 +4890,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122756445</v>
+        <v>122757367</v>
       </c>
       <c r="B42" t="n">
         <v>57478</v>
@@ -4910,10 +4935,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585841</v>
+        <v>585662</v>
       </c>
       <c r="R42" t="n">
-        <v>7059850</v>
+        <v>7059890</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4945,7 +4970,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4955,7 +4980,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -4987,7 +5012,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122757637</v>
+        <v>122757680</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5032,13 +5057,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585636</v>
+        <v>585688</v>
       </c>
       <c r="R43" t="n">
-        <v>7059970</v>
+        <v>7059983</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5065,24 +5090,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5097,22 +5112,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122758139</v>
+        <v>122757549</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5125,42 +5140,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585743</v>
+        <v>585660</v>
       </c>
       <c r="R44" t="n">
-        <v>7059982</v>
+        <v>7059938</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5187,24 +5197,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5219,22 +5214,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122757549</v>
+        <v>122758139</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,37 +5242,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585660</v>
+        <v>585743</v>
       </c>
       <c r="R45" t="n">
-        <v>7059938</v>
+        <v>7059982</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5304,9 +5304,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5321,22 +5336,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122757492</v>
+        <v>122755167</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5349,16 +5364,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5378,13 +5393,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585665</v>
+        <v>585967</v>
       </c>
       <c r="R46" t="n">
-        <v>7059914</v>
+        <v>7059854</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5411,24 +5426,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5443,19 +5443,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122755167</v>
+        <v>122755221</v>
       </c>
       <c r="B47" t="n">
         <v>57494</v>
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585967</v>
+        <v>585897</v>
       </c>
       <c r="R47" t="n">
-        <v>7059854</v>
+        <v>7059846</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -4300,10 +4300,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122757908</v>
+        <v>122758257</v>
       </c>
       <c r="B37" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4316,37 +4316,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585747</v>
+        <v>585735</v>
       </c>
       <c r="R37" t="n">
-        <v>7059980</v>
+        <v>7059987</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4373,19 +4378,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:14</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4400,22 +4400,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122756445</v>
+        <v>122757908</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4428,39 +4428,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>585841</v>
+        <v>585747</v>
       </c>
       <c r="R38" t="n">
-        <v>7059850</v>
+        <v>7059980</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4492,7 +4487,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4502,12 +4497,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:57</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4534,7 +4524,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122757492</v>
+        <v>122757637</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -4579,10 +4569,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>585665</v>
+        <v>585636</v>
       </c>
       <c r="R39" t="n">
-        <v>7059914</v>
+        <v>7059970</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4614,7 +4604,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4624,7 +4614,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4656,10 +4646,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122757637</v>
+        <v>122757549</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4672,42 +4662,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585636</v>
+        <v>585660</v>
       </c>
       <c r="R40" t="n">
-        <v>7059970</v>
+        <v>7059938</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4734,24 +4719,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4766,19 +4736,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122758257</v>
+        <v>122757492</v>
       </c>
       <c r="B41" t="n">
         <v>57478</v>
@@ -4814,7 +4784,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4823,13 +4793,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585735</v>
+        <v>585665</v>
       </c>
       <c r="R41" t="n">
-        <v>7059987</v>
+        <v>7059914</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4856,14 +4826,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4878,22 +4858,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122757367</v>
+        <v>122755167</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4906,16 +4886,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4935,13 +4915,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585662</v>
+        <v>585967</v>
       </c>
       <c r="R42" t="n">
-        <v>7059890</v>
+        <v>7059854</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4968,24 +4948,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5000,19 +4965,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122757680</v>
+        <v>122756445</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5057,13 +5022,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585688</v>
+        <v>585841</v>
       </c>
       <c r="R43" t="n">
-        <v>7059983</v>
+        <v>7059850</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5090,14 +5055,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5112,22 +5087,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122757549</v>
+        <v>122757680</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5140,34 +5115,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585660</v>
+        <v>585688</v>
       </c>
       <c r="R44" t="n">
-        <v>7059938</v>
+        <v>7059983</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5200,6 +5180,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5348,10 +5333,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122755167</v>
+        <v>122757367</v>
       </c>
       <c r="B46" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5364,16 +5349,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5393,13 +5378,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585967</v>
+        <v>585662</v>
       </c>
       <c r="R46" t="n">
-        <v>7059854</v>
+        <v>7059890</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5426,9 +5411,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5443,12 +5443,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -4870,10 +4870,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122755167</v>
+        <v>122756445</v>
       </c>
       <c r="B42" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4886,16 +4886,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4915,13 +4915,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585967</v>
+        <v>585841</v>
       </c>
       <c r="R42" t="n">
-        <v>7059854</v>
+        <v>7059850</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4948,9 +4948,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4965,22 +4980,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122756445</v>
+        <v>122755167</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4993,16 +5008,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5022,13 +5037,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585841</v>
+        <v>585967</v>
       </c>
       <c r="R43" t="n">
-        <v>7059850</v>
+        <v>7059854</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5055,24 +5070,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5087,12 +5087,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -4300,10 +4300,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122758257</v>
+        <v>122757549</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4316,39 +4316,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585735</v>
+        <v>585660</v>
       </c>
       <c r="R37" t="n">
-        <v>7059987</v>
+        <v>7059938</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4381,11 +4376,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4524,7 +4514,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122757637</v>
+        <v>122756445</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -4569,10 +4559,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>585636</v>
+        <v>585841</v>
       </c>
       <c r="R39" t="n">
-        <v>7059970</v>
+        <v>7059850</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4604,7 +4594,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4614,7 +4604,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4646,10 +4636,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122757549</v>
+        <v>122758257</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4662,34 +4652,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585660</v>
+        <v>585735</v>
       </c>
       <c r="R40" t="n">
-        <v>7059938</v>
+        <v>7059987</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4722,6 +4717,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4748,7 +4748,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122757492</v>
+        <v>122757680</v>
       </c>
       <c r="B41" t="n">
         <v>57478</v>
@@ -4793,13 +4793,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585665</v>
+        <v>585688</v>
       </c>
       <c r="R41" t="n">
-        <v>7059914</v>
+        <v>7059983</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4826,24 +4826,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4858,22 +4848,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122756445</v>
+        <v>122755167</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4886,16 +4876,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4915,13 +4905,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585841</v>
+        <v>585967</v>
       </c>
       <c r="R42" t="n">
-        <v>7059850</v>
+        <v>7059854</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4948,24 +4938,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4980,19 +4955,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122755167</v>
+        <v>122755221</v>
       </c>
       <c r="B43" t="n">
         <v>57494</v>
@@ -5037,10 +5012,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585967</v>
+        <v>585897</v>
       </c>
       <c r="R43" t="n">
-        <v>7059854</v>
+        <v>7059846</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5099,7 +5074,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122757680</v>
+        <v>122758139</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5144,13 +5119,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585688</v>
+        <v>585743</v>
       </c>
       <c r="R44" t="n">
-        <v>7059983</v>
+        <v>7059982</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5177,14 +5152,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5199,19 +5184,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122758139</v>
+        <v>122757367</v>
       </c>
       <c r="B45" t="n">
         <v>57478</v>
@@ -5256,10 +5241,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585743</v>
+        <v>585662</v>
       </c>
       <c r="R45" t="n">
-        <v>7059982</v>
+        <v>7059890</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5291,7 +5276,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5301,7 +5286,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5333,7 +5318,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122757367</v>
+        <v>122757637</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5378,10 +5363,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585662</v>
+        <v>585636</v>
       </c>
       <c r="R46" t="n">
-        <v>7059890</v>
+        <v>7059970</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5413,7 +5398,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5423,7 +5408,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5455,10 +5440,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122755221</v>
+        <v>122757492</v>
       </c>
       <c r="B47" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5471,16 +5456,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5500,13 +5485,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585897</v>
+        <v>585665</v>
       </c>
       <c r="R47" t="n">
-        <v>7059846</v>
+        <v>7059914</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5533,9 +5518,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5550,12 +5550,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -4300,10 +4300,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122757549</v>
+        <v>122757367</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4316,37 +4316,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585660</v>
+        <v>585662</v>
       </c>
       <c r="R37" t="n">
-        <v>7059938</v>
+        <v>7059890</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4373,9 +4378,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4390,22 +4410,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122757908</v>
+        <v>122757637</v>
       </c>
       <c r="B38" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4418,34 +4438,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>585747</v>
+        <v>585636</v>
       </c>
       <c r="R38" t="n">
-        <v>7059980</v>
+        <v>7059970</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4477,7 +4502,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4487,7 +4512,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4514,7 +4544,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122756445</v>
+        <v>122758139</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -4559,10 +4589,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>585841</v>
+        <v>585743</v>
       </c>
       <c r="R39" t="n">
-        <v>7059850</v>
+        <v>7059982</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4594,7 +4624,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4604,7 +4634,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4636,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122758257</v>
+        <v>122757549</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4652,39 +4682,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585735</v>
+        <v>585660</v>
       </c>
       <c r="R40" t="n">
-        <v>7059987</v>
+        <v>7059938</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4717,11 +4742,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4748,10 +4768,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122757680</v>
+        <v>122755221</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4764,16 +4784,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4793,10 +4813,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585688</v>
+        <v>585897</v>
       </c>
       <c r="R41" t="n">
-        <v>7059983</v>
+        <v>7059846</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4829,11 +4849,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4967,10 +4982,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122755221</v>
+        <v>122757908</v>
       </c>
       <c r="B43" t="n">
-        <v>57494</v>
+        <v>82553</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4983,42 +4998,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585897</v>
+        <v>585747</v>
       </c>
       <c r="R43" t="n">
-        <v>7059846</v>
+        <v>7059980</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5045,9 +5055,19 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5062,19 +5082,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122758139</v>
+        <v>122756445</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5119,10 +5139,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585743</v>
+        <v>585841</v>
       </c>
       <c r="R44" t="n">
-        <v>7059982</v>
+        <v>7059850</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5154,7 +5174,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5164,7 +5184,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5196,7 +5216,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122757367</v>
+        <v>122758257</v>
       </c>
       <c r="B45" t="n">
         <v>57478</v>
@@ -5232,7 +5252,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5241,13 +5261,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585662</v>
+        <v>585735</v>
       </c>
       <c r="R45" t="n">
-        <v>7059890</v>
+        <v>7059987</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5274,24 +5294,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5306,19 +5316,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122757637</v>
+        <v>122757680</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5363,13 +5373,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585636</v>
+        <v>585688</v>
       </c>
       <c r="R46" t="n">
-        <v>7059970</v>
+        <v>7059983</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5396,24 +5406,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5428,12 +5428,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -4300,10 +4300,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122757367</v>
+        <v>122757549</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4316,42 +4316,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585662</v>
+        <v>585660</v>
       </c>
       <c r="R37" t="n">
-        <v>7059890</v>
+        <v>7059938</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4378,24 +4373,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4410,22 +4390,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122757637</v>
+        <v>122755221</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4438,16 +4418,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4467,13 +4447,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>585636</v>
+        <v>585897</v>
       </c>
       <c r="R38" t="n">
-        <v>7059970</v>
+        <v>7059846</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4500,24 +4480,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4532,19 +4497,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122758139</v>
+        <v>122757637</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -4589,10 +4554,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>585743</v>
+        <v>585636</v>
       </c>
       <c r="R39" t="n">
-        <v>7059982</v>
+        <v>7059970</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4624,7 +4589,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4634,7 +4599,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4666,10 +4631,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122757549</v>
+        <v>122756445</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4682,37 +4647,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585660</v>
+        <v>585841</v>
       </c>
       <c r="R40" t="n">
-        <v>7059938</v>
+        <v>7059850</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4739,9 +4709,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4756,22 +4741,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122755221</v>
+        <v>122757680</v>
       </c>
       <c r="B41" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4784,16 +4769,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4813,10 +4798,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585897</v>
+        <v>585688</v>
       </c>
       <c r="R41" t="n">
-        <v>7059846</v>
+        <v>7059983</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4849,6 +4834,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4875,10 +4865,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122755167</v>
+        <v>122757492</v>
       </c>
       <c r="B42" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4891,16 +4881,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4920,13 +4910,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585967</v>
+        <v>585665</v>
       </c>
       <c r="R42" t="n">
-        <v>7059854</v>
+        <v>7059914</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4953,9 +4943,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4970,22 +4975,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122757908</v>
+        <v>122758257</v>
       </c>
       <c r="B43" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4998,37 +5003,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585747</v>
+        <v>585735</v>
       </c>
       <c r="R43" t="n">
-        <v>7059980</v>
+        <v>7059987</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5055,19 +5065,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:14</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5082,22 +5087,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122756445</v>
+        <v>122755167</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5110,16 +5115,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5139,13 +5144,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585841</v>
+        <v>585967</v>
       </c>
       <c r="R44" t="n">
-        <v>7059850</v>
+        <v>7059854</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5172,24 +5177,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5204,22 +5194,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122758257</v>
+        <v>122757908</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5232,42 +5222,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585735</v>
+        <v>585747</v>
       </c>
       <c r="R45" t="n">
-        <v>7059987</v>
+        <v>7059980</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5294,14 +5279,19 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5316,19 +5306,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122757680</v>
+        <v>122757367</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5373,13 +5363,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585688</v>
+        <v>585662</v>
       </c>
       <c r="R46" t="n">
-        <v>7059983</v>
+        <v>7059890</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5406,14 +5396,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5428,19 +5428,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122757492</v>
+        <v>122758139</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585665</v>
+        <v>585743</v>
       </c>
       <c r="R47" t="n">
-        <v>7059914</v>
+        <v>7059982</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -4300,10 +4300,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122757549</v>
+        <v>122757492</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4316,37 +4316,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585660</v>
+        <v>585665</v>
       </c>
       <c r="R37" t="n">
-        <v>7059938</v>
+        <v>7059914</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4373,9 +4378,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4390,22 +4410,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122755221</v>
+        <v>122757637</v>
       </c>
       <c r="B38" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4418,16 +4438,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4447,13 +4467,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>585897</v>
+        <v>585636</v>
       </c>
       <c r="R38" t="n">
-        <v>7059846</v>
+        <v>7059970</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4480,9 +4500,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4497,19 +4532,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122757637</v>
+        <v>122757367</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -4554,10 +4589,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>585636</v>
+        <v>585662</v>
       </c>
       <c r="R39" t="n">
-        <v>7059970</v>
+        <v>7059890</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4589,7 +4624,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4599,7 +4634,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4631,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122756445</v>
+        <v>122757549</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4647,42 +4682,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585841</v>
+        <v>585660</v>
       </c>
       <c r="R40" t="n">
-        <v>7059850</v>
+        <v>7059938</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4709,24 +4739,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4741,22 +4756,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122757680</v>
+        <v>122757908</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4769,42 +4784,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585688</v>
+        <v>585747</v>
       </c>
       <c r="R41" t="n">
-        <v>7059983</v>
+        <v>7059980</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4831,14 +4841,19 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4853,22 +4868,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122757492</v>
+        <v>122755167</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4881,16 +4896,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4910,13 +4925,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585665</v>
+        <v>585967</v>
       </c>
       <c r="R42" t="n">
-        <v>7059914</v>
+        <v>7059854</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4943,24 +4958,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4975,19 +4975,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122758257</v>
+        <v>122756445</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5023,7 +5023,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5032,13 +5032,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585735</v>
+        <v>585841</v>
       </c>
       <c r="R43" t="n">
-        <v>7059987</v>
+        <v>7059850</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5065,14 +5065,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5087,19 +5097,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122755167</v>
+        <v>122755221</v>
       </c>
       <c r="B44" t="n">
         <v>57494</v>
@@ -5144,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585967</v>
+        <v>585897</v>
       </c>
       <c r="R44" t="n">
-        <v>7059854</v>
+        <v>7059846</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5206,10 +5216,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122757908</v>
+        <v>122758257</v>
       </c>
       <c r="B45" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5222,37 +5232,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585747</v>
+        <v>585735</v>
       </c>
       <c r="R45" t="n">
-        <v>7059980</v>
+        <v>7059987</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5279,19 +5294,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:14</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5306,19 +5316,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122757367</v>
+        <v>122758139</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5363,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585662</v>
+        <v>585743</v>
       </c>
       <c r="R46" t="n">
-        <v>7059890</v>
+        <v>7059982</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5398,7 +5408,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5408,7 +5418,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5440,7 +5450,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122758139</v>
+        <v>122757680</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -5485,13 +5495,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585743</v>
+        <v>585688</v>
       </c>
       <c r="R47" t="n">
-        <v>7059982</v>
+        <v>7059983</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5518,24 +5528,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5550,12 +5550,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -4300,10 +4300,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122757492</v>
+        <v>122755167</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4316,16 +4316,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4345,13 +4345,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585665</v>
+        <v>585967</v>
       </c>
       <c r="R37" t="n">
-        <v>7059914</v>
+        <v>7059854</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4378,24 +4378,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4410,19 +4395,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122757637</v>
+        <v>122757492</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -4467,10 +4452,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>585636</v>
+        <v>585665</v>
       </c>
       <c r="R38" t="n">
-        <v>7059970</v>
+        <v>7059914</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4502,7 +4487,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4512,7 +4497,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4544,10 +4529,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122757367</v>
+        <v>122755221</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4560,16 +4545,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4589,13 +4574,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>585662</v>
+        <v>585897</v>
       </c>
       <c r="R39" t="n">
-        <v>7059890</v>
+        <v>7059846</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4622,24 +4607,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4654,22 +4624,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122757549</v>
+        <v>122756445</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4682,37 +4652,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585660</v>
+        <v>585841</v>
       </c>
       <c r="R40" t="n">
-        <v>7059938</v>
+        <v>7059850</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4739,9 +4714,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4756,22 +4746,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122757908</v>
+        <v>122757680</v>
       </c>
       <c r="B41" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4784,37 +4774,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585747</v>
+        <v>585688</v>
       </c>
       <c r="R41" t="n">
-        <v>7059980</v>
+        <v>7059983</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4841,19 +4836,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:14</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4868,22 +4858,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122755167</v>
+        <v>122757549</v>
       </c>
       <c r="B42" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4896,39 +4886,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585967</v>
+        <v>585660</v>
       </c>
       <c r="R42" t="n">
-        <v>7059854</v>
+        <v>7059938</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4987,7 +4972,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122756445</v>
+        <v>122758139</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5032,10 +5017,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585841</v>
+        <v>585743</v>
       </c>
       <c r="R43" t="n">
-        <v>7059850</v>
+        <v>7059982</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5067,7 +5052,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5077,7 +5062,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -5109,10 +5094,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122755221</v>
+        <v>122757637</v>
       </c>
       <c r="B44" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5125,16 +5110,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5154,13 +5139,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585897</v>
+        <v>585636</v>
       </c>
       <c r="R44" t="n">
-        <v>7059846</v>
+        <v>7059970</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5187,9 +5172,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5204,12 +5204,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5328,7 +5328,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122758139</v>
+        <v>122757367</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585743</v>
+        <v>585662</v>
       </c>
       <c r="R46" t="n">
-        <v>7059982</v>
+        <v>7059890</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5450,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122757680</v>
+        <v>122757908</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5466,42 +5466,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585688</v>
+        <v>585747</v>
       </c>
       <c r="R47" t="n">
-        <v>7059983</v>
+        <v>7059980</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5528,14 +5523,19 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5550,12 +5550,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -4758,10 +4758,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122757680</v>
+        <v>122757549</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4774,39 +4774,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585688</v>
+        <v>585660</v>
       </c>
       <c r="R41" t="n">
-        <v>7059983</v>
+        <v>7059938</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4839,11 +4834,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4870,10 +4860,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122757549</v>
+        <v>122757680</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4886,34 +4876,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585660</v>
+        <v>585688</v>
       </c>
       <c r="R42" t="n">
-        <v>7059938</v>
+        <v>7059983</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4946,6 +4941,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -4300,10 +4300,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122755167</v>
+        <v>122757549</v>
       </c>
       <c r="B37" t="n">
-        <v>57494</v>
+        <v>78769</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4316,39 +4316,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585967</v>
+        <v>585660</v>
       </c>
       <c r="R37" t="n">
-        <v>7059854</v>
+        <v>7059938</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4407,10 +4402,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122757492</v>
+        <v>122758139</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4452,10 +4447,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>585665</v>
+        <v>585743</v>
       </c>
       <c r="R38" t="n">
-        <v>7059914</v>
+        <v>7059982</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4487,7 +4482,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4497,7 +4492,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4529,10 +4524,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122755221</v>
+        <v>122756445</v>
       </c>
       <c r="B39" t="n">
-        <v>57494</v>
+        <v>57481</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4545,16 +4540,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4574,13 +4569,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>585897</v>
+        <v>585841</v>
       </c>
       <c r="R39" t="n">
-        <v>7059846</v>
+        <v>7059850</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4607,9 +4602,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4624,22 +4634,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122756445</v>
+        <v>122757680</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4681,13 +4691,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585841</v>
+        <v>585688</v>
       </c>
       <c r="R40" t="n">
-        <v>7059850</v>
+        <v>7059983</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4714,24 +4724,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4746,22 +4746,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122757549</v>
+        <v>122757637</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4774,37 +4774,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585660</v>
+        <v>585636</v>
       </c>
       <c r="R41" t="n">
-        <v>7059938</v>
+        <v>7059970</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4831,9 +4836,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4848,22 +4868,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122757680</v>
+        <v>122757492</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4905,13 +4925,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585688</v>
+        <v>585665</v>
       </c>
       <c r="R42" t="n">
-        <v>7059983</v>
+        <v>7059914</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4938,14 +4958,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4960,22 +4990,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122758139</v>
+        <v>122755221</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>57497</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4988,16 +5018,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5017,13 +5047,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>585743</v>
+        <v>585897</v>
       </c>
       <c r="R43" t="n">
-        <v>7059982</v>
+        <v>7059846</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5050,24 +5080,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5082,22 +5097,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122757637</v>
+        <v>122757367</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5139,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585636</v>
+        <v>585662</v>
       </c>
       <c r="R44" t="n">
-        <v>7059970</v>
+        <v>7059890</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5174,7 +5189,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5184,7 +5199,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5216,10 +5231,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122758257</v>
+        <v>122757908</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>82556</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5232,42 +5247,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585735</v>
+        <v>585747</v>
       </c>
       <c r="R45" t="n">
-        <v>7059987</v>
+        <v>7059980</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5294,14 +5304,19 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5316,22 +5331,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122757367</v>
+        <v>122755167</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>57497</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5344,16 +5359,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5373,13 +5388,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585662</v>
+        <v>585967</v>
       </c>
       <c r="R46" t="n">
-        <v>7059890</v>
+        <v>7059854</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5406,24 +5421,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5438,22 +5438,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122757908</v>
+        <v>122758257</v>
       </c>
       <c r="B47" t="n">
-        <v>82553</v>
+        <v>57481</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5466,37 +5466,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>585747</v>
+        <v>585735</v>
       </c>
       <c r="R47" t="n">
-        <v>7059980</v>
+        <v>7059987</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5523,19 +5528,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:14</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5550,12 +5550,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -4300,10 +4300,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122757549</v>
+        <v>122758139</v>
       </c>
       <c r="B37" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4316,37 +4316,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>585660</v>
+        <v>585743</v>
       </c>
       <c r="R37" t="n">
-        <v>7059938</v>
+        <v>7059982</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4373,9 +4378,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4390,19 +4410,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122758139</v>
+        <v>122757492</v>
       </c>
       <c r="B38" t="n">
         <v>57481</v>
@@ -4447,10 +4467,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>585743</v>
+        <v>585665</v>
       </c>
       <c r="R38" t="n">
-        <v>7059982</v>
+        <v>7059914</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4482,7 +4502,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4492,7 +4512,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4646,10 +4666,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122757680</v>
+        <v>122757908</v>
       </c>
       <c r="B40" t="n">
-        <v>57481</v>
+        <v>82558</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4662,42 +4682,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>585688</v>
+        <v>585747</v>
       </c>
       <c r="R40" t="n">
-        <v>7059983</v>
+        <v>7059980</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4724,14 +4739,19 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4746,19 +4766,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122757637</v>
+        <v>122757680</v>
       </c>
       <c r="B41" t="n">
         <v>57481</v>
@@ -4803,13 +4823,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>585636</v>
+        <v>585688</v>
       </c>
       <c r="R41" t="n">
-        <v>7059970</v>
+        <v>7059983</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4836,24 +4856,14 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4868,22 +4878,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122757492</v>
+        <v>122755167</v>
       </c>
       <c r="B42" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4896,16 +4906,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4925,13 +4935,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>585665</v>
+        <v>585967</v>
       </c>
       <c r="R42" t="n">
-        <v>7059914</v>
+        <v>7059854</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4958,24 +4968,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4990,12 +4985,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5109,10 +5104,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122757367</v>
+        <v>122757549</v>
       </c>
       <c r="B44" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5125,42 +5120,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>585662</v>
+        <v>585660</v>
       </c>
       <c r="R44" t="n">
-        <v>7059890</v>
+        <v>7059938</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5187,24 +5177,9 @@
           <t>2025-02-25</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5219,22 +5194,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122757908</v>
+        <v>122757637</v>
       </c>
       <c r="B45" t="n">
-        <v>82556</v>
+        <v>57481</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5247,34 +5222,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>585747</v>
+        <v>585636</v>
       </c>
       <c r="R45" t="n">
-        <v>7059980</v>
+        <v>7059970</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5306,7 +5286,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5316,7 +5296,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5343,10 +5328,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122755167</v>
+        <v>122757367</v>
       </c>
       <c r="B46" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5359,16 +5344,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5388,13 +5373,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>585967</v>
+        <v>585662</v>
       </c>
       <c r="R46" t="n">
-        <v>7059854</v>
+        <v>7059890</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5421,9 +5406,24 @@
           <t>2025-02-25</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5438,12 +5438,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5560,6 +5560,842 @@
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125265495</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>585672</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7059874</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125265038</v>
+      </c>
+      <c r="B49" t="n">
+        <v>96227</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>585638</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7059956</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125265762</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>585766</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7059797</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125265649</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>585700</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7059842</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125265666</v>
+      </c>
+      <c r="B52" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>585701</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7059838</v>
+      </c>
+      <c r="S52" t="n">
+        <v>15</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125265105</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>585633</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7059942</v>
+      </c>
+      <c r="S53" t="n">
+        <v>15</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125265916</v>
+      </c>
+      <c r="B54" t="n">
+        <v>56112</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>585837</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7059893</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125265542</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91361</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>585673</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7059863</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -5562,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125265495</v>
+        <v>125265542</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5574,25 +5574,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585672</v>
+        <v>585673</v>
       </c>
       <c r="R48" t="n">
-        <v>7059874</v>
+        <v>7059863</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5664,10 +5664,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125265038</v>
+        <v>125265495</v>
       </c>
       <c r="B49" t="n">
-        <v>96227</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5676,25 +5676,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585638</v>
+        <v>585672</v>
       </c>
       <c r="R49" t="n">
-        <v>7059956</v>
+        <v>7059874</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5766,10 +5766,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125265762</v>
+        <v>125265666</v>
       </c>
       <c r="B50" t="n">
-        <v>57529</v>
+        <v>90977</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5778,43 +5778,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585766</v>
+        <v>585701</v>
       </c>
       <c r="R50" t="n">
-        <v>7059797</v>
+        <v>7059838</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5873,10 +5868,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125265649</v>
+        <v>125265038</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>96227</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5885,25 +5880,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5913,10 +5908,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585700</v>
+        <v>585638</v>
       </c>
       <c r="R51" t="n">
-        <v>7059842</v>
+        <v>7059956</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5975,10 +5970,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125265666</v>
+        <v>125265762</v>
       </c>
       <c r="B52" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5987,38 +5982,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585701</v>
+        <v>585766</v>
       </c>
       <c r="R52" t="n">
-        <v>7059838</v>
+        <v>7059797</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6296,10 +6296,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265542</v>
+        <v>125265649</v>
       </c>
       <c r="B55" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6308,25 +6308,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585673</v>
+        <v>585700</v>
       </c>
       <c r="R55" t="n">
-        <v>7059863</v>
+        <v>7059842</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -5562,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125265542</v>
+        <v>125265495</v>
       </c>
       <c r="B48" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5574,25 +5574,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585673</v>
+        <v>585672</v>
       </c>
       <c r="R48" t="n">
-        <v>7059863</v>
+        <v>7059874</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5664,7 +5664,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125265495</v>
+        <v>125265649</v>
       </c>
       <c r="B49" t="n">
         <v>91012</v>
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585672</v>
+        <v>585700</v>
       </c>
       <c r="R49" t="n">
-        <v>7059874</v>
+        <v>7059842</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5766,10 +5766,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125265666</v>
+        <v>125265762</v>
       </c>
       <c r="B50" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5778,38 +5778,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585701</v>
+        <v>585766</v>
       </c>
       <c r="R50" t="n">
-        <v>7059838</v>
+        <v>7059797</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5868,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125265038</v>
+        <v>125265916</v>
       </c>
       <c r="B51" t="n">
-        <v>96227</v>
+        <v>56112</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5880,38 +5885,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>206004</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585638</v>
+        <v>585837</v>
       </c>
       <c r="R51" t="n">
-        <v>7059956</v>
+        <v>7059893</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5970,10 +5980,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125265762</v>
+        <v>125265038</v>
       </c>
       <c r="B52" t="n">
-        <v>57529</v>
+        <v>96227</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5982,43 +5992,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585766</v>
+        <v>585638</v>
       </c>
       <c r="R52" t="n">
-        <v>7059797</v>
+        <v>7059956</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6077,10 +6082,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125265105</v>
+        <v>125265666</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6089,43 +6094,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585633</v>
+        <v>585701</v>
       </c>
       <c r="R53" t="n">
-        <v>7059942</v>
+        <v>7059838</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6158,11 +6158,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6189,10 +6184,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265916</v>
+        <v>125265105</v>
       </c>
       <c r="B54" t="n">
-        <v>56112</v>
+        <v>57513</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6205,27 +6200,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>gående/springande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6234,10 +6229,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585837</v>
+        <v>585633</v>
       </c>
       <c r="R54" t="n">
-        <v>7059893</v>
+        <v>7059942</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6270,6 +6265,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6296,10 +6296,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265649</v>
+        <v>125265542</v>
       </c>
       <c r="B55" t="n">
-        <v>91012</v>
+        <v>91361</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6308,25 +6308,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585700</v>
+        <v>585673</v>
       </c>
       <c r="R55" t="n">
-        <v>7059842</v>
+        <v>7059863</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -5562,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125265495</v>
+        <v>125265762</v>
       </c>
       <c r="B48" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5578,34 +5578,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585672</v>
+        <v>585766</v>
       </c>
       <c r="R48" t="n">
-        <v>7059874</v>
+        <v>7059797</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5664,7 +5669,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125265649</v>
+        <v>125265495</v>
       </c>
       <c r="B49" t="n">
         <v>91012</v>
@@ -5704,10 +5709,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585700</v>
+        <v>585672</v>
       </c>
       <c r="R49" t="n">
-        <v>7059842</v>
+        <v>7059874</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5766,10 +5771,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125265762</v>
+        <v>125265916</v>
       </c>
       <c r="B50" t="n">
-        <v>57529</v>
+        <v>56112</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5782,27 +5787,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gående/springande</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5811,10 +5816,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585766</v>
+        <v>585837</v>
       </c>
       <c r="R50" t="n">
-        <v>7059797</v>
+        <v>7059893</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5873,10 +5878,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125265916</v>
+        <v>125265666</v>
       </c>
       <c r="B51" t="n">
-        <v>56112</v>
+        <v>90977</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5885,43 +5890,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>206004</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585837</v>
+        <v>585701</v>
       </c>
       <c r="R51" t="n">
-        <v>7059893</v>
+        <v>7059838</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5980,10 +5980,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125265038</v>
+        <v>125265105</v>
       </c>
       <c r="B52" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5992,38 +5992,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585638</v>
+        <v>585633</v>
       </c>
       <c r="R52" t="n">
-        <v>7059956</v>
+        <v>7059942</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6056,6 +6061,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6082,10 +6092,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125265666</v>
+        <v>125265038</v>
       </c>
       <c r="B53" t="n">
-        <v>90977</v>
+        <v>96227</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6098,21 +6108,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6122,10 +6132,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585701</v>
+        <v>585638</v>
       </c>
       <c r="R53" t="n">
-        <v>7059838</v>
+        <v>7059956</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6184,10 +6194,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265105</v>
+        <v>125265542</v>
       </c>
       <c r="B54" t="n">
-        <v>57513</v>
+        <v>91361</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6196,43 +6206,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585633</v>
+        <v>585673</v>
       </c>
       <c r="R54" t="n">
-        <v>7059942</v>
+        <v>7059863</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6265,11 +6270,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6296,10 +6296,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265542</v>
+        <v>125265649</v>
       </c>
       <c r="B55" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6308,25 +6308,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585673</v>
+        <v>585700</v>
       </c>
       <c r="R55" t="n">
-        <v>7059863</v>
+        <v>7059842</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -5562,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125265762</v>
+        <v>125265542</v>
       </c>
       <c r="B48" t="n">
-        <v>57529</v>
+        <v>91361</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5574,43 +5574,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585766</v>
+        <v>585673</v>
       </c>
       <c r="R48" t="n">
-        <v>7059797</v>
+        <v>7059863</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5669,10 +5664,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125265495</v>
+        <v>125265666</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5681,25 +5676,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5709,10 +5704,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585672</v>
+        <v>585701</v>
       </c>
       <c r="R49" t="n">
-        <v>7059874</v>
+        <v>7059838</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5878,10 +5873,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125265666</v>
+        <v>125265495</v>
       </c>
       <c r="B51" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5890,25 +5885,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5913,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585701</v>
+        <v>585672</v>
       </c>
       <c r="R51" t="n">
-        <v>7059838</v>
+        <v>7059874</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5980,10 +5975,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125265105</v>
+        <v>125265649</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5996,39 +5991,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585633</v>
+        <v>585700</v>
       </c>
       <c r="R52" t="n">
-        <v>7059942</v>
+        <v>7059842</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6061,11 +6051,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6092,10 +6077,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125265038</v>
+        <v>125265105</v>
       </c>
       <c r="B53" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6104,38 +6089,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585638</v>
+        <v>585633</v>
       </c>
       <c r="R53" t="n">
-        <v>7059956</v>
+        <v>7059942</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6168,6 +6158,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6194,10 +6189,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265542</v>
+        <v>125265038</v>
       </c>
       <c r="B54" t="n">
-        <v>91361</v>
+        <v>96227</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6206,25 +6201,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2062</v>
+        <v>2869</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6234,10 +6229,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585673</v>
+        <v>585638</v>
       </c>
       <c r="R54" t="n">
-        <v>7059863</v>
+        <v>7059956</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6296,10 +6291,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265649</v>
+        <v>125265762</v>
       </c>
       <c r="B55" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6312,34 +6307,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585700</v>
+        <v>585766</v>
       </c>
       <c r="R55" t="n">
-        <v>7059842</v>
+        <v>7059797</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -6077,10 +6077,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125265105</v>
+        <v>125265038</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6089,43 +6089,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585633</v>
+        <v>585638</v>
       </c>
       <c r="R53" t="n">
-        <v>7059942</v>
+        <v>7059956</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6158,11 +6153,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6189,10 +6179,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265038</v>
+        <v>125265105</v>
       </c>
       <c r="B54" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6201,38 +6191,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585638</v>
+        <v>585633</v>
       </c>
       <c r="R54" t="n">
-        <v>7059956</v>
+        <v>7059942</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6265,6 +6260,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -5562,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125265542</v>
+        <v>125265105</v>
       </c>
       <c r="B48" t="n">
-        <v>91361</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5574,38 +5574,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585673</v>
+        <v>585633</v>
       </c>
       <c r="R48" t="n">
-        <v>7059863</v>
+        <v>7059942</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5638,6 +5643,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5664,10 +5674,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125265666</v>
+        <v>125265762</v>
       </c>
       <c r="B49" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5676,38 +5686,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585701</v>
+        <v>585766</v>
       </c>
       <c r="R49" t="n">
-        <v>7059838</v>
+        <v>7059797</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5766,10 +5781,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125265916</v>
+        <v>125265038</v>
       </c>
       <c r="B50" t="n">
-        <v>56112</v>
+        <v>96227</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5778,43 +5793,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>206004</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585837</v>
+        <v>585638</v>
       </c>
       <c r="R50" t="n">
-        <v>7059893</v>
+        <v>7059956</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5873,10 +5883,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125265495</v>
+        <v>125265916</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>56112</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5889,34 +5899,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>206004</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585672</v>
+        <v>585837</v>
       </c>
       <c r="R51" t="n">
-        <v>7059874</v>
+        <v>7059893</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6077,10 +6092,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125265038</v>
+        <v>125265542</v>
       </c>
       <c r="B53" t="n">
-        <v>96227</v>
+        <v>91361</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6089,25 +6104,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2869</v>
+        <v>2062</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6117,10 +6132,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585638</v>
+        <v>585673</v>
       </c>
       <c r="R53" t="n">
-        <v>7059956</v>
+        <v>7059863</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6179,10 +6194,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265105</v>
+        <v>125265666</v>
       </c>
       <c r="B54" t="n">
-        <v>57513</v>
+        <v>90977</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6191,43 +6206,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585633</v>
+        <v>585701</v>
       </c>
       <c r="R54" t="n">
-        <v>7059942</v>
+        <v>7059838</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6260,11 +6270,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6291,10 +6296,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265762</v>
+        <v>125265495</v>
       </c>
       <c r="B55" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6307,39 +6312,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585766</v>
+        <v>585672</v>
       </c>
       <c r="R55" t="n">
-        <v>7059797</v>
+        <v>7059874</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -5562,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125265105</v>
+        <v>125265666</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>91131</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5574,43 +5574,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585633</v>
+        <v>585701</v>
       </c>
       <c r="R48" t="n">
-        <v>7059942</v>
+        <v>7059838</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5643,11 +5638,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5674,10 +5664,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125265762</v>
+        <v>125265105</v>
       </c>
       <c r="B49" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5690,16 +5680,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5710,7 +5700,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5719,10 +5709,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585766</v>
+        <v>585633</v>
       </c>
       <c r="R49" t="n">
-        <v>7059797</v>
+        <v>7059942</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5755,6 +5745,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5781,10 +5776,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125265038</v>
+        <v>125265762</v>
       </c>
       <c r="B50" t="n">
-        <v>96227</v>
+        <v>57632</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5793,38 +5788,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585638</v>
+        <v>585766</v>
       </c>
       <c r="R50" t="n">
-        <v>7059956</v>
+        <v>7059797</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5886,7 +5886,7 @@
         <v>125265916</v>
       </c>
       <c r="B51" t="n">
-        <v>56112</v>
+        <v>56226</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125265649</v>
+        <v>125265542</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
+        <v>91521</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6002,25 +6002,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585700</v>
+        <v>585673</v>
       </c>
       <c r="R52" t="n">
-        <v>7059842</v>
+        <v>7059863</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6092,10 +6092,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125265542</v>
+        <v>125265038</v>
       </c>
       <c r="B53" t="n">
-        <v>91361</v>
+        <v>96395</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6104,25 +6104,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2062</v>
+        <v>2869</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6132,10 +6132,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585673</v>
+        <v>585638</v>
       </c>
       <c r="R53" t="n">
-        <v>7059863</v>
+        <v>7059956</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6194,10 +6194,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265666</v>
+        <v>125265495</v>
       </c>
       <c r="B54" t="n">
-        <v>90977</v>
+        <v>91166</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6206,25 +6206,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585701</v>
+        <v>585672</v>
       </c>
       <c r="R54" t="n">
-        <v>7059838</v>
+        <v>7059874</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6296,10 +6296,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265495</v>
+        <v>125265649</v>
       </c>
       <c r="B55" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585672</v>
+        <v>585700</v>
       </c>
       <c r="R55" t="n">
-        <v>7059874</v>
+        <v>7059842</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -5562,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125265666</v>
+        <v>125265105</v>
       </c>
       <c r="B48" t="n">
-        <v>91131</v>
+        <v>57635</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5574,38 +5574,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585701</v>
+        <v>585633</v>
       </c>
       <c r="R48" t="n">
-        <v>7059838</v>
+        <v>7059942</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5638,6 +5643,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5664,10 +5674,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125265105</v>
+        <v>125265762</v>
       </c>
       <c r="B49" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5680,16 +5690,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5700,7 +5710,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5709,10 +5719,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585633</v>
+        <v>585766</v>
       </c>
       <c r="R49" t="n">
-        <v>7059942</v>
+        <v>7059797</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5745,11 +5755,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5776,10 +5781,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125265762</v>
+        <v>125265666</v>
       </c>
       <c r="B50" t="n">
-        <v>57632</v>
+        <v>91131</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5788,43 +5793,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585766</v>
+        <v>585701</v>
       </c>
       <c r="R50" t="n">
-        <v>7059797</v>
+        <v>7059838</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125265542</v>
+        <v>125265495</v>
       </c>
       <c r="B52" t="n">
-        <v>91521</v>
+        <v>91166</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6002,25 +6002,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585673</v>
+        <v>585672</v>
       </c>
       <c r="R52" t="n">
-        <v>7059863</v>
+        <v>7059874</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6092,10 +6092,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125265038</v>
+        <v>125265542</v>
       </c>
       <c r="B53" t="n">
-        <v>96395</v>
+        <v>91521</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6104,25 +6104,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2869</v>
+        <v>2062</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6132,10 +6132,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585638</v>
+        <v>585673</v>
       </c>
       <c r="R53" t="n">
-        <v>7059956</v>
+        <v>7059863</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6194,10 +6194,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265495</v>
+        <v>125265038</v>
       </c>
       <c r="B54" t="n">
-        <v>91166</v>
+        <v>96395</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6206,25 +6206,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585672</v>
+        <v>585638</v>
       </c>
       <c r="R54" t="n">
-        <v>7059874</v>
+        <v>7059956</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -6194,10 +6194,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265038</v>
+        <v>125265649</v>
       </c>
       <c r="B54" t="n">
-        <v>96395</v>
+        <v>91166</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6206,25 +6206,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585638</v>
+        <v>585700</v>
       </c>
       <c r="R54" t="n">
-        <v>7059956</v>
+        <v>7059842</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6296,10 +6296,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265649</v>
+        <v>125265038</v>
       </c>
       <c r="B55" t="n">
-        <v>91166</v>
+        <v>96395</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6308,25 +6308,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585700</v>
+        <v>585638</v>
       </c>
       <c r="R55" t="n">
-        <v>7059842</v>
+        <v>7059956</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -5562,15 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125265105</v>
+        <v>125265495</v>
       </c>
       <c r="B48" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5578,39 +5573,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>585633</v>
+        <v>585672</v>
       </c>
       <c r="R48" t="n">
-        <v>7059942</v>
+        <v>7059874</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5643,11 +5633,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5674,15 +5659,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125265762</v>
+        <v>125265649</v>
       </c>
       <c r="B49" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5690,39 +5670,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>585766</v>
+        <v>585700</v>
       </c>
       <c r="R49" t="n">
-        <v>7059797</v>
+        <v>7059842</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5781,15 +5756,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125265666</v>
+        <v>125265038</v>
       </c>
       <c r="B50" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5797,21 +5767,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5821,10 +5791,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>585701</v>
+        <v>585638</v>
       </c>
       <c r="R50" t="n">
-        <v>7059838</v>
+        <v>7059956</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5883,15 +5853,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125265916</v>
+        <v>125265105</v>
       </c>
       <c r="B51" t="n">
-        <v>56226</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5899,27 +5864,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>gående/springande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5928,10 +5893,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>585837</v>
+        <v>585633</v>
       </c>
       <c r="R51" t="n">
-        <v>7059893</v>
+        <v>7059942</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5964,6 +5929,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Gamla ringhack, gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5990,37 +5960,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125265495</v>
+        <v>125265542</v>
       </c>
       <c r="B52" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91575</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +5995,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>585672</v>
+        <v>585673</v>
       </c>
       <c r="R52" t="n">
-        <v>7059874</v>
+        <v>7059863</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6092,50 +6057,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125265542</v>
+        <v>125265762</v>
       </c>
       <c r="B53" t="n">
-        <v>91521</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2062</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585673</v>
+        <v>585766</v>
       </c>
       <c r="R53" t="n">
-        <v>7059863</v>
+        <v>7059797</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6194,15 +6159,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265649</v>
+        <v>125265916</v>
       </c>
       <c r="B54" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56227</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6210,34 +6170,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>206004</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sör-Tågsjöberget, Sör-Tågsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585700</v>
+        <v>585837</v>
       </c>
       <c r="R54" t="n">
-        <v>7059842</v>
+        <v>7059893</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6296,15 +6261,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125265038</v>
+        <v>125265666</v>
       </c>
       <c r="B55" t="n">
-        <v>96395</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6312,21 +6272,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6336,10 +6296,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>585638</v>
+        <v>585701</v>
       </c>
       <c r="R55" t="n">
-        <v>7059956</v>
+        <v>7059838</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -5565,7 +5565,7 @@
         <v>125265495</v>
       </c>
       <c r="B48" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>125265649</v>
       </c>
       <c r="B49" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>125265038</v>
       </c>
       <c r="B50" t="n">
-        <v>96450</v>
+        <v>96457</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>125265542</v>
       </c>
       <c r="B52" t="n">
-        <v>91575</v>
+        <v>91582</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>125265666</v>
       </c>
       <c r="B55" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -5565,7 +5565,7 @@
         <v>125265495</v>
       </c>
       <c r="B48" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>125265649</v>
       </c>
       <c r="B49" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>125265038</v>
       </c>
       <c r="B50" t="n">
-        <v>96457</v>
+        <v>96460</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>125265542</v>
       </c>
       <c r="B52" t="n">
-        <v>91582</v>
+        <v>91586</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6057,10 +6057,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125265762</v>
+        <v>125265916</v>
       </c>
       <c r="B53" t="n">
-        <v>57648</v>
+        <v>56227</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6068,27 +6068,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gående/springande</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6097,10 +6097,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>585766</v>
+        <v>585837</v>
       </c>
       <c r="R53" t="n">
-        <v>7059797</v>
+        <v>7059893</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6159,10 +6159,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125265916</v>
+        <v>125265762</v>
       </c>
       <c r="B54" t="n">
-        <v>56227</v>
+        <v>57648</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6170,27 +6170,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>206004</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>gående/springande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>585837</v>
+        <v>585766</v>
       </c>
       <c r="R54" t="n">
-        <v>7059893</v>
+        <v>7059797</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6264,7 +6264,7 @@
         <v>125265666</v>
       </c>
       <c r="B55" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6356,6 +6356,107 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126074348</v>
+      </c>
+      <c r="B56" t="n">
+        <v>88641</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>510</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Tågsjöberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>585779</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7059930</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -6361,7 +6361,7 @@
         <v>126074348</v>
       </c>
       <c r="B56" t="n">
-        <v>88641</v>
+        <v>88643</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -6361,7 +6361,7 @@
         <v>126074348</v>
       </c>
       <c r="B56" t="n">
-        <v>88643</v>
+        <v>88645</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -6361,7 +6361,7 @@
         <v>126074348</v>
       </c>
       <c r="B56" t="n">
-        <v>88645</v>
+        <v>88647</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -6361,7 +6361,7 @@
         <v>126074348</v>
       </c>
       <c r="B56" t="n">
-        <v>88647</v>
+        <v>88651</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 9626-2021 artfynd.xlsx
+++ b/artfynd/A 9626-2021 artfynd.xlsx
@@ -6361,7 +6361,7 @@
         <v>126074348</v>
       </c>
       <c r="B56" t="n">
-        <v>88651</v>
+        <v>88654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
